--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96665</v>
+        <v>96668</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96665</v>
+        <v>96668</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96668</v>
+        <v>96669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96668</v>
+        <v>96669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96669</v>
+        <v>96674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96669</v>
+        <v>96674</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
